--- a/lonas.xlsx
+++ b/lonas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pabloviggiano/Desktop/Carpas/Nueva App Dangiola/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB05D0B9-A721-7745-8A13-8029B18287B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56827A22-CDF4-1E48-9862-D914751005B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{796DABE2-0C73-5145-823D-869795FB07CB}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="23040" windowHeight="8480" xr2:uid="{796DABE2-0C73-5145-823D-869795FB07CB}"/>
   </bookViews>
   <sheets>
     <sheet name="LONAS" sheetId="1" r:id="rId1"/>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
     </ext>
@@ -39,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="34">
   <si>
     <t>Color</t>
   </si>
@@ -96,18 +85,70 @@
   </si>
   <si>
     <t>Lonas</t>
+  </si>
+  <si>
+    <t>12x5</t>
+  </si>
+  <si>
+    <t>15x5</t>
+  </si>
+  <si>
+    <t>20x5</t>
+  </si>
+  <si>
+    <t>8x3</t>
+  </si>
+  <si>
+    <t>6x3</t>
+  </si>
+  <si>
+    <t>5x5</t>
+  </si>
+  <si>
+    <t>3x3</t>
+  </si>
+  <si>
+    <t>Blanco - Pagoda</t>
+  </si>
+  <si>
+    <t>Negro - Pagoda</t>
+  </si>
+  <si>
+    <t>Cristal/Blanco - Pagoda</t>
+  </si>
+  <si>
+    <t>Cristal/Negro - Pagoda</t>
+  </si>
+  <si>
+    <t>30x5</t>
+  </si>
+  <si>
+    <t>40x5</t>
+  </si>
+  <si>
+    <t>4x4</t>
+  </si>
+  <si>
+    <t>4x3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -131,8 +172,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,26 +515,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{289A7D4E-F8FE-E54A-B34E-A4A94DD9D521}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="5" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -494,16 +543,16 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -511,16 +560,16 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="1">
+        <v>20</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -528,16 +577,16 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="1">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -545,16 +594,16 @@
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="1">
+        <v>20</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -562,16 +611,16 @@
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1">
+        <v>20</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -579,16 +628,16 @@
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7">
-        <v>20</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1">
+        <v>20</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -596,16 +645,16 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8">
-        <v>20</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -613,16 +662,16 @@
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1">
+        <v>20</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -630,16 +679,16 @@
       <c r="A10" t="s">
         <v>4</v>
       </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10">
-        <v>10</v>
-      </c>
-      <c r="D10">
-        <v>20</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="1">
+        <v>20</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -647,16 +696,16 @@
       <c r="A11" t="s">
         <v>7</v>
       </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11">
-        <v>10</v>
-      </c>
-      <c r="D11">
-        <v>20</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="1">
+        <v>20</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -664,16 +713,16 @@
       <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12">
-        <v>10</v>
-      </c>
-      <c r="D12">
-        <v>20</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="1">
+        <v>20</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -681,16 +730,16 @@
       <c r="A13" t="s">
         <v>9</v>
       </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13">
-        <v>10</v>
-      </c>
-      <c r="D13">
-        <v>20</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="B13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="1">
+        <v>20</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -698,16 +747,16 @@
       <c r="A14" t="s">
         <v>4</v>
       </c>
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14">
-        <v>20</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="B14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="1">
+        <v>20</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -715,16 +764,16 @@
       <c r="A15" t="s">
         <v>7</v>
       </c>
-      <c r="B15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15">
-        <v>20</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="B15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="1">
+        <v>20</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -732,16 +781,16 @@
       <c r="A16" t="s">
         <v>8</v>
       </c>
-      <c r="B16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16">
-        <v>20</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="1">
+        <v>20</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -749,16 +798,16 @@
       <c r="A17" t="s">
         <v>9</v>
       </c>
-      <c r="B17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17">
-        <v>20</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="B17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="1">
+        <v>20</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -766,16 +815,16 @@
       <c r="A18" t="s">
         <v>4</v>
       </c>
-      <c r="B18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18">
-        <v>20</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="B18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="1">
+        <v>20</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -783,16 +832,16 @@
       <c r="A19" t="s">
         <v>7</v>
       </c>
-      <c r="B19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19">
-        <v>20</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="B19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="1">
+        <v>20</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -800,16 +849,16 @@
       <c r="A20" t="s">
         <v>8</v>
       </c>
-      <c r="B20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20">
-        <v>20</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="B20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="1">
+        <v>20</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -817,16 +866,16 @@
       <c r="A21" t="s">
         <v>9</v>
       </c>
-      <c r="B21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21">
-        <v>20</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="B21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="1">
+        <v>20</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -834,16 +883,16 @@
       <c r="A22" t="s">
         <v>4</v>
       </c>
-      <c r="B22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22">
-        <v>20</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="B22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="1">
+        <v>20</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -851,16 +900,16 @@
       <c r="A23" t="s">
         <v>7</v>
       </c>
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23">
-        <v>20</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="B23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="1">
+        <v>20</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -868,16 +917,16 @@
       <c r="A24" t="s">
         <v>8</v>
       </c>
-      <c r="B24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24">
-        <v>20</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="B24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="1">
+        <v>20</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -885,16 +934,16 @@
       <c r="A25" t="s">
         <v>9</v>
       </c>
-      <c r="B25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25">
-        <v>20</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="B25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="1">
+        <v>20</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -902,16 +951,16 @@
       <c r="A26" t="s">
         <v>4</v>
       </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26">
-        <v>20</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="B26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="1">
+        <v>20</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -919,16 +968,16 @@
       <c r="A27" t="s">
         <v>7</v>
       </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27">
-        <v>20</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="B27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="1">
+        <v>20</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -936,16 +985,16 @@
       <c r="A28" t="s">
         <v>8</v>
       </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28">
-        <v>20</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="B28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="1">
+        <v>20</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -953,16 +1002,16 @@
       <c r="A29" t="s">
         <v>9</v>
       </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29">
-        <v>20</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="B29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="1">
+        <v>20</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -970,16 +1019,16 @@
       <c r="A30" t="s">
         <v>4</v>
       </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30">
-        <v>20</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="B30" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="1">
+        <v>20</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -987,16 +1036,16 @@
       <c r="A31" t="s">
         <v>7</v>
       </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31">
-        <v>20</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="B31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="1">
+        <v>20</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1004,16 +1053,16 @@
       <c r="A32" t="s">
         <v>8</v>
       </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32">
-        <v>20</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="B32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="1">
+        <v>20</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1021,20 +1070,1721 @@
       <c r="A33" t="s">
         <v>9</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="1">
+        <v>20</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="1">
+        <v>20</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" s="1">
+        <v>20</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" s="1">
+        <v>20</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" s="1">
+        <v>20</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" s="1">
+        <v>20</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" s="1">
+        <v>20</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="1">
+        <v>20</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" s="1">
+        <v>20</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>26</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="1">
+        <v>20</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>27</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43" s="1">
+        <v>20</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" s="1">
+        <v>20</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D45" s="1">
+        <v>20</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D46" s="1">
+        <v>20</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D47" s="1">
+        <v>20</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" s="1">
+        <v>20</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" s="1">
+        <v>20</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="1">
+        <v>20</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="1">
+        <v>20</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="1">
+        <v>20</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="1">
+        <v>20</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="1">
+        <v>20</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="1">
+        <v>20</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="1">
+        <v>20</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="1">
+        <v>20</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" s="1">
+        <v>20</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" s="1">
+        <v>20</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D60" s="1">
+        <v>20</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" s="1">
+        <v>20</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="1">
+        <v>20</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" s="1">
+        <v>20</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="1">
+        <v>20</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="1">
+        <v>20</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D66" s="1">
+        <v>20</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>7</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D67" s="1">
+        <v>20</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D68" s="1">
+        <v>20</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>9</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D69" s="1">
+        <v>20</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D70" s="1">
+        <v>20</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D71" s="1">
+        <v>20</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>8</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D72" s="1">
+        <v>20</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>9</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D73" s="1">
+        <v>20</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D74" s="1">
+        <v>20</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D75" s="1">
+        <v>20</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>8</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D76" s="1">
+        <v>20</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>9</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D77" s="1">
+        <v>20</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" s="1">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1">
+        <v>20</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>7</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" s="1">
+        <v>3</v>
+      </c>
+      <c r="D79" s="1">
+        <v>20</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>8</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80" s="1">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1">
+        <v>20</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>9</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" s="1">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1">
+        <v>20</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>4</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82" s="1">
+        <v>6</v>
+      </c>
+      <c r="D82" s="1">
+        <v>20</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>7</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83" s="1">
+        <v>6</v>
+      </c>
+      <c r="D83" s="1">
+        <v>20</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C84" s="1">
+        <v>6</v>
+      </c>
+      <c r="D84" s="1">
+        <v>20</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>9</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C85" s="1">
+        <v>6</v>
+      </c>
+      <c r="D85" s="1">
+        <v>20</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>4</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C86" s="1">
+        <v>8</v>
+      </c>
+      <c r="D86" s="1">
+        <v>20</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C87" s="1">
+        <v>8</v>
+      </c>
+      <c r="D87" s="1">
+        <v>20</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>8</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C88" s="1">
+        <v>8</v>
+      </c>
+      <c r="D88" s="1">
+        <v>20</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>9</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89" s="1">
+        <v>8</v>
+      </c>
+      <c r="D89" s="1">
+        <v>20</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>4</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C90" s="1">
+        <v>10</v>
+      </c>
+      <c r="D90" s="1">
+        <v>20</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>7</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C91" s="1">
+        <v>10</v>
+      </c>
+      <c r="D91" s="1">
+        <v>20</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>8</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C92" s="1">
+        <v>10</v>
+      </c>
+      <c r="D92" s="1">
+        <v>20</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>9</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93" s="1">
+        <v>10</v>
+      </c>
+      <c r="D93" s="1">
+        <v>20</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>4</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C94" s="1">
+        <v>12</v>
+      </c>
+      <c r="D94" s="1">
+        <v>20</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>7</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C95" s="1">
+        <v>12</v>
+      </c>
+      <c r="D95" s="1">
+        <v>20</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>8</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C96" s="1">
+        <v>12</v>
+      </c>
+      <c r="D96" s="1">
+        <v>20</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>9</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C97" s="1">
+        <v>12</v>
+      </c>
+      <c r="D97" s="1">
+        <v>20</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>4</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C98" s="1">
+        <v>15</v>
+      </c>
+      <c r="D98" s="1">
+        <v>20</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>7</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C99" s="1">
+        <v>15</v>
+      </c>
+      <c r="D99" s="1">
+        <v>20</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>8</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C100" s="1">
+        <v>15</v>
+      </c>
+      <c r="D100" s="1">
+        <v>20</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C101" s="1">
+        <v>15</v>
+      </c>
+      <c r="D101" s="1">
+        <v>20</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>4</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102" s="1">
+        <v>20</v>
+      </c>
+      <c r="D102" s="1">
+        <v>20</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>7</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C103" s="1">
+        <v>20</v>
+      </c>
+      <c r="D103" s="1">
+        <v>20</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>8</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C104" s="1">
+        <v>20</v>
+      </c>
+      <c r="D104" s="1">
+        <v>20</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>9</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C105" s="1">
+        <v>20</v>
+      </c>
+      <c r="D105" s="1">
+        <v>20</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>4</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C106" s="1">
+        <v>30</v>
+      </c>
+      <c r="D106" s="1">
+        <v>20</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>7</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C107" s="1">
+        <v>30</v>
+      </c>
+      <c r="D107" s="1">
+        <v>20</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>8</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C108" s="1">
+        <v>30</v>
+      </c>
+      <c r="D108" s="1">
+        <v>20</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>9</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C109" s="1">
+        <v>30</v>
+      </c>
+      <c r="D109" s="1">
+        <v>20</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>4</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" s="1">
+        <v>40</v>
+      </c>
+      <c r="D110" s="1">
+        <v>20</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>7</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C111" s="1">
+        <v>40</v>
+      </c>
+      <c r="D111" s="1">
+        <v>20</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>8</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C112" s="1">
+        <v>40</v>
+      </c>
+      <c r="D112" s="1">
+        <v>20</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>9</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C113" s="1">
+        <v>40</v>
+      </c>
+      <c r="D113" s="1">
+        <v>20</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>4</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C114" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D114" s="1">
+        <v>20</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>7</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D115" s="1">
+        <v>20</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>8</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D116" s="1">
+        <v>20</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>9</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D117" s="1">
+        <v>20</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>4</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D33">
-        <v>20</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="D118" s="1">
+        <v>20</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>7</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D119" s="1">
+        <v>20</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>8</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D120" s="1">
+        <v>20</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>9</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D121" s="1">
+        <v>20</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>4</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D122" s="1">
+        <v>20</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>7</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D123" s="1">
+        <v>20</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>8</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D124" s="1">
+        <v>20</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>9</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D125" s="1">
+        <v>20</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>4</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D126" s="1">
+        <v>20</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>7</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D127" s="1">
+        <v>20</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>8</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D128" s="1">
+        <v>20</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>9</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D129" s="1">
+        <v>20</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>4</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D130" s="1">
+        <v>20</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>7</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D131" s="1">
+        <v>20</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>8</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D132" s="1">
+        <v>20</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>9</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D133" s="1">
+        <v>20</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>